--- a/test_orders_surabaya3.xlsx
+++ b/test_orders_surabaya3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\KULIAH\Magang\routing_kurir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2493C86E-FCD1-4DBA-8AE9-45F980BE263C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC508A2-C34A-44FB-96F3-A73B98F1FB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,9 +441,6 @@
     <t>Numan</t>
   </si>
   <si>
-    <t>Jl. Gebang Putih, Keputih, Kec. Sukolilo, Surabaya, Jawa Timur 60117</t>
-  </si>
-  <si>
     <t>Jl. Cantian Tengah IV 34-10, Sidodadi, Kec. Simokerto, Surabaya, Jawa Timur 60145</t>
   </si>
   <si>
@@ -469,6 +466,9 @@
   </si>
   <si>
     <t>Hotel Platinum Tunjungan Surabaya, Jl. Tunjungan No.11 - 21, Genteng, Kec. Genteng, Surabaya, Jawa Timur 60275</t>
+  </si>
+  <si>
+    <t>Jl. Gebang Putih No.115, Gebang Putih, Kec. Sukolilo, Surabaya, Jawa Timur 60117</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1084,7 @@
         <v>64</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="AU2" s="2" t="s">
         <v>65</v>
@@ -1178,7 +1178,7 @@
         <v>74</v>
       </c>
       <c r="AT3" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AU3" s="3" t="s">
         <v>65</v>
@@ -1272,7 +1272,7 @@
         <v>83</v>
       </c>
       <c r="AT4" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AU4" s="2" t="s">
         <v>65</v>
@@ -1366,7 +1366,7 @@
         <v>92</v>
       </c>
       <c r="AT5" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AU5" s="3" t="s">
         <v>65</v>
@@ -1460,7 +1460,7 @@
         <v>101</v>
       </c>
       <c r="AT6" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AU6" s="2" t="s">
         <v>65</v>
@@ -1554,7 +1554,7 @@
         <v>112</v>
       </c>
       <c r="AT7" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AU7" s="3" t="s">
         <v>65</v>
@@ -1648,7 +1648,7 @@
         <v>121</v>
       </c>
       <c r="AT8" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AU8" s="2" t="s">
         <v>65</v>
@@ -1742,7 +1742,7 @@
         <v>130</v>
       </c>
       <c r="AT9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AU9" s="3" t="s">
         <v>65</v>
@@ -1836,7 +1836,7 @@
         <v>121</v>
       </c>
       <c r="AT10" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AU10" s="2" t="s">
         <v>65</v>
@@ -1930,7 +1930,7 @@
         <v>130</v>
       </c>
       <c r="AT11" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AU11" s="3" t="s">
         <v>65</v>

--- a/test_orders_surabaya3.xlsx
+++ b/test_orders_surabaya3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\KULIAH\Magang\routing_kurir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC508A2-C34A-44FB-96F3-A73B98F1FB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE56516C-5D43-421C-9BC3-A1CB83FBDA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="149">
   <si>
     <t>SO Number</t>
   </si>
@@ -469,6 +469,15 @@
   </si>
   <si>
     <t>Jl. Gebang Putih No.115, Gebang Putih, Kec. Sukolilo, Surabaya, Jawa Timur 60117</t>
+  </si>
+  <si>
+    <t>Jl. Raya Putat Lor No.183, Prambon, Boboh, Kec. Menganti, Kabupaten Gresik, Jawa Timur 61174</t>
+  </si>
+  <si>
+    <t>Yohana</t>
+  </si>
+  <si>
+    <t>Dusun Banjarsari, Banjaran, Kec. Driyorejo, Kabupaten Gresik, Jawa Timur 61177</t>
   </si>
 </sst>
 </file>
@@ -838,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV11"/>
+  <dimension ref="A1:AV13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1939,6 +1948,194 @@
         <v>132</v>
       </c>
     </row>
+    <row r="12" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="3"/>
+      <c r="AQ12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>146</v>
+      </c>
+      <c r="AU12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV12" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="3"/>
+      <c r="AQ13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AR13" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV13" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test_orders_surabaya3.xlsx
+++ b/test_orders_surabaya3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\KULIAH\Magang\routing_kurir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE56516C-5D43-421C-9BC3-A1CB83FBDA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273B430C-5482-4041-97E6-85A25EAB5620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="177">
   <si>
     <t>SO Number</t>
   </si>
@@ -478,6 +478,90 @@
   </si>
   <si>
     <t>Dusun Banjarsari, Banjaran, Kec. Driyorejo, Kabupaten Gresik, Jawa Timur 61177</t>
+  </si>
+  <si>
+    <t>Renta</t>
+  </si>
+  <si>
+    <t>Panjang (cm)</t>
+  </si>
+  <si>
+    <t>Lebar (cm)</t>
+  </si>
+  <si>
+    <t>Tinggi (cm)</t>
+  </si>
+  <si>
+    <t>Berat (kg)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>19.5</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>5.0</t>
   </si>
 </sst>
 </file>
@@ -534,16 +618,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -847,22 +934,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="27" width="14" customWidth="1"/>
-    <col min="28" max="28" width="35" customWidth="1"/>
-    <col min="29" max="43" width="14" customWidth="1"/>
-    <col min="44" max="44" width="20" customWidth="1"/>
-    <col min="45" max="45" width="14" customWidth="1"/>
-    <col min="46" max="46" width="60" customWidth="1"/>
-    <col min="47" max="48" width="14" customWidth="1"/>
+    <col min="1" max="1" width="15" style="2" customWidth="1"/>
+    <col min="2" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20" style="2" customWidth="1"/>
+    <col min="6" max="27" width="14" style="2" customWidth="1"/>
+    <col min="28" max="28" width="35" style="2" customWidth="1"/>
+    <col min="29" max="43" width="14" style="2" customWidth="1"/>
+    <col min="44" max="44" width="20" style="2" customWidth="1"/>
+    <col min="45" max="45" width="14" style="2" customWidth="1"/>
+    <col min="46" max="46" width="60" style="2" customWidth="1"/>
+    <col min="47" max="48" width="14" style="2" customWidth="1"/>
+    <col min="49" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1007,1134 +1095,1339 @@
       <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="AW1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="2" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2" t="s">
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2" t="s">
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AS2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AU2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AV2" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="AW2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
-    <row r="3" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="s">
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3" t="s">
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
-      <c r="AQ3" s="3" t="s">
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AR3" s="3" t="s">
+      <c r="AR3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AS3" s="3" t="s">
+      <c r="AS3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AT3" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="AU3" s="3" t="s">
+      <c r="AU3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AV3" s="3" t="s">
+      <c r="AV3" s="4" t="s">
         <v>75</v>
       </c>
+      <c r="AW3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
-    <row r="4" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2" t="s">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2" t="s">
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AB4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AC4" s="2" t="s">
+      <c r="AC4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AD4" s="2" t="s">
+      <c r="AD4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AE4" s="2" t="s">
+      <c r="AE4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AF4" s="2" t="s">
+      <c r="AF4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="2" t="s">
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2" t="s">
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="3"/>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AR4" s="2" t="s">
+      <c r="AR4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AS4" s="2" t="s">
+      <c r="AS4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AT4" s="2" t="s">
+      <c r="AT4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AU4" s="2" t="s">
+      <c r="AU4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AV4" s="2" t="s">
+      <c r="AV4" s="3" t="s">
         <v>84</v>
       </c>
+      <c r="AW4" s="2">
+        <v>60</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AZ4" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="5" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3" t="s">
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3" t="s">
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="AB5" s="3" t="s">
+      <c r="AB5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AC5" s="3" t="s">
+      <c r="AC5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AD5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AE5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AF5" s="3" t="s">
+      <c r="AF5" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AG5" s="3"/>
-      <c r="AH5" s="3" t="s">
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
-      <c r="AO5" s="3"/>
-      <c r="AP5" s="3"/>
-      <c r="AQ5" s="3" t="s">
+      <c r="AI5" s="4"/>
+      <c r="AJ5" s="4"/>
+      <c r="AK5" s="4"/>
+      <c r="AL5" s="4"/>
+      <c r="AM5" s="4"/>
+      <c r="AN5" s="4"/>
+      <c r="AO5" s="4"/>
+      <c r="AP5" s="4"/>
+      <c r="AQ5" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AR5" s="3" t="s">
+      <c r="AR5" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AS5" s="3" t="s">
+      <c r="AS5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AT5" s="3" t="s">
+      <c r="AT5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="AU5" s="3" t="s">
+      <c r="AU5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AV5" s="3" t="s">
+      <c r="AV5" s="4" t="s">
         <v>93</v>
       </c>
+      <c r="AW5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
-    <row r="6" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2" t="s">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2" t="s">
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AB6" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AC6" s="2" t="s">
+      <c r="AC6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AD6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AE6" s="2" t="s">
+      <c r="AE6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AF6" s="2" t="s">
+      <c r="AF6" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2" t="s">
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2" t="s">
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AR6" s="2" t="s">
+      <c r="AR6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AS6" s="2" t="s">
+      <c r="AS6" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AT6" s="2" t="s">
+      <c r="AT6" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AU6" s="2" t="s">
+      <c r="AU6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AV6" s="2" t="s">
+      <c r="AV6" s="3" t="s">
         <v>102</v>
       </c>
+      <c r="AW6" s="2">
+        <v>90</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
-    <row r="7" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3" t="s">
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3" t="s">
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="AB7" s="3" t="s">
+      <c r="AB7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="AC7" s="3" t="s">
+      <c r="AC7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AD7" s="3" t="s">
+      <c r="AD7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE7" s="3" t="s">
+      <c r="AE7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="AF7" s="3" t="s">
+      <c r="AF7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="AG7" s="3"/>
-      <c r="AH7" s="3" t="s">
+      <c r="AG7" s="4"/>
+      <c r="AH7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="AI7" s="3"/>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="3"/>
-      <c r="AM7" s="3"/>
-      <c r="AN7" s="3"/>
-      <c r="AO7" s="3"/>
-      <c r="AP7" s="3"/>
-      <c r="AQ7" s="3" t="s">
+      <c r="AI7" s="4"/>
+      <c r="AJ7" s="4"/>
+      <c r="AK7" s="4"/>
+      <c r="AL7" s="4"/>
+      <c r="AM7" s="4"/>
+      <c r="AN7" s="4"/>
+      <c r="AO7" s="4"/>
+      <c r="AP7" s="4"/>
+      <c r="AQ7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="AR7" s="3" t="s">
+      <c r="AR7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="AS7" s="3" t="s">
+      <c r="AS7" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="AT7" s="3" t="s">
+      <c r="AT7" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="AU7" s="3" t="s">
+      <c r="AU7" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AV7" s="3" t="s">
+      <c r="AV7" s="4" t="s">
         <v>113</v>
       </c>
+      <c r="AW7" s="2">
+        <v>45</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="AY7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AZ7" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="8" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2" t="s">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2" t="s">
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AB8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="AC8" s="2" t="s">
+      <c r="AC8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AD8" s="2" t="s">
+      <c r="AD8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AE8" s="2" t="s">
+      <c r="AE8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AF8" s="2" t="s">
+      <c r="AF8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AG8" s="2"/>
-      <c r="AH8" s="2" t="s">
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2" t="s">
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AR8" s="2" t="s">
+      <c r="AR8" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AS8" s="2" t="s">
+      <c r="AS8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="AT8" s="2" t="s">
+      <c r="AT8" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AU8" s="2" t="s">
+      <c r="AU8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AV8" s="2" t="s">
+      <c r="AV8" s="3" t="s">
         <v>122</v>
       </c>
+      <c r="AW8" s="2">
+        <v>75</v>
+      </c>
+      <c r="AX8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AY8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AZ8" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="9" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3" t="s">
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB9" s="3" t="s">
+      <c r="AB9" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AC9" s="3" t="s">
+      <c r="AC9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AD9" s="3" t="s">
+      <c r="AD9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE9" s="3" t="s">
+      <c r="AE9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AF9" s="3" t="s">
+      <c r="AF9" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="3" t="s">
+      <c r="AG9" s="4"/>
+      <c r="AH9" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="3"/>
-      <c r="AQ9" s="3" t="s">
+      <c r="AI9" s="4"/>
+      <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
+      <c r="AL9" s="4"/>
+      <c r="AM9" s="4"/>
+      <c r="AN9" s="4"/>
+      <c r="AO9" s="4"/>
+      <c r="AP9" s="4"/>
+      <c r="AQ9" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AR9" s="3" t="s">
+      <c r="AR9" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="AS9" s="3" t="s">
+      <c r="AS9" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="AT9" s="3" t="s">
+      <c r="AT9" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="AU9" s="3" t="s">
+      <c r="AU9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AV9" s="3" t="s">
+      <c r="AV9" s="4" t="s">
         <v>131</v>
       </c>
+      <c r="AW9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AX9" s="2">
+        <v>45</v>
+      </c>
+      <c r="AY9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AZ9" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
-    <row r="10" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2" t="s">
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="2" t="s">
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AB10" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="AC10" s="2" t="s">
+      <c r="AC10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AD10" s="2" t="s">
+      <c r="AD10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AE10" s="2" t="s">
+      <c r="AE10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AF10" s="2" t="s">
+      <c r="AF10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AG10" s="2"/>
-      <c r="AH10" s="2" t="s">
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-      <c r="AK10" s="2"/>
-      <c r="AL10" s="2"/>
-      <c r="AM10" s="2"/>
-      <c r="AN10" s="2"/>
-      <c r="AO10" s="2"/>
-      <c r="AP10" s="2"/>
-      <c r="AQ10" s="2" t="s">
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
+      <c r="AQ10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AR10" s="2" t="s">
+      <c r="AR10" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AS10" s="2" t="s">
+      <c r="AS10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="AT10" s="2" t="s">
+      <c r="AT10" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="AU10" s="2" t="s">
+      <c r="AU10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AV10" s="2" t="s">
+      <c r="AV10" s="3" t="s">
         <v>133</v>
       </c>
+      <c r="AW10" s="2">
+        <v>45</v>
+      </c>
+      <c r="AX10" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="AY10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AZ10" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
-    <row r="11" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3" t="s">
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3" t="s">
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB11" s="3" t="s">
+      <c r="AB11" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AC11" s="3" t="s">
+      <c r="AC11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AD11" s="3" t="s">
+      <c r="AD11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE11" s="3" t="s">
+      <c r="AE11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AF11" s="3" t="s">
+      <c r="AF11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3" t="s">
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="3"/>
-      <c r="AQ11" s="3" t="s">
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AR11" s="3" t="s">
+      <c r="AR11" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AS11" s="3" t="s">
+      <c r="AS11" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="AT11" s="3" t="s">
+      <c r="AT11" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="AU11" s="3" t="s">
+      <c r="AU11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AV11" s="3" t="s">
+      <c r="AV11" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="AW11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AX11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AY11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AZ11" s="2">
+        <v>25</v>
+      </c>
     </row>
-    <row r="12" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3" t="s">
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3" t="s">
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB12" s="3" t="s">
+      <c r="AB12" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AC12" s="3" t="s">
+      <c r="AC12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AD12" s="3" t="s">
+      <c r="AD12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE12" s="3" t="s">
+      <c r="AE12" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AF12" s="3" t="s">
+      <c r="AF12" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AG12" s="3"/>
-      <c r="AH12" s="3" t="s">
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="3"/>
-      <c r="AQ12" s="3" t="s">
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="4"/>
+      <c r="AM12" s="4"/>
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AR12" s="3" t="s">
+      <c r="AR12" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="AS12" s="3" t="s">
+      <c r="AS12" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="AT12" t="s">
+      <c r="AT12" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AU12" s="3" t="s">
+      <c r="AU12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AV12" s="3" t="s">
+      <c r="AV12" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="AW12" s="2">
+        <v>90</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="AY12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AZ12" s="2">
+        <v>35</v>
+      </c>
     </row>
-    <row r="13" spans="1:48" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3" t="s">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3" t="s">
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AB13" s="3" t="s">
+      <c r="AB13" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AC13" s="3" t="s">
+      <c r="AC13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AD13" s="3" t="s">
+      <c r="AD13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AE13" s="3" t="s">
+      <c r="AE13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AF13" s="3" t="s">
+      <c r="AF13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3" t="s">
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
-      <c r="AQ13" s="3" t="s">
+      <c r="AI13" s="4"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+      <c r="AL13" s="4"/>
+      <c r="AM13" s="4"/>
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="4"/>
+      <c r="AQ13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AR13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="AS13" s="3" t="s">
+      <c r="AR13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AS13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="AT13" t="s">
+      <c r="AT13" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="AU13" s="3" t="s">
+      <c r="AU13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AV13" s="3" t="s">
+      <c r="AV13" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="AW13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AZ13" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="3"/>
+      <c r="AQ14" s="3"/>
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="3"/>
+      <c r="AU14" s="3"/>
+      <c r="AV14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
